--- a/data/trans_dic/LAWTONB_2R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,2; 20,9</t>
+          <t>11,94; 20,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,32; 19,44</t>
+          <t>11,45; 20,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 13,52</t>
+          <t>7,09; 13,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 17,01</t>
+          <t>11,12; 17,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 24,61</t>
+          <t>16,02; 24,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,25; 26,14</t>
+          <t>16,86; 26,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,56; 27,9</t>
+          <t>18,11; 26,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 21,11</t>
+          <t>17,65; 23,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,77</t>
+          <t>15,22; 21,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,31; 21,33</t>
+          <t>15,38; 21,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,87; 19,13</t>
+          <t>13,75; 19,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 18,02</t>
+          <t>15,33; 19,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,98; 46,68</t>
+          <t>33,88; 47,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,67; 48,59</t>
+          <t>34,77; 48,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,31; 40,62</t>
+          <t>29,85; 41,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,55; 44,89</t>
+          <t>34,47; 43,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,24; 54,61</t>
+          <t>43,54; 54,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,15; 59,83</t>
+          <t>49,13; 59,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,76; 54,33</t>
+          <t>42,56; 53,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,23; 64,45</t>
+          <t>57,52; 64,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,06; 50,11</t>
+          <t>41,54; 50,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,33; 53,64</t>
+          <t>45,44; 53,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,29; 47,6</t>
+          <t>39,29; 47,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,03; 55,57</t>
+          <t>49,36; 54,9</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,92; 30,44</t>
+          <t>22,74; 30,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,81; 30,81</t>
+          <t>22,85; 30,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,87; 24,34</t>
+          <t>17,9; 24,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,59; 28,07</t>
+          <t>22,38; 27,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,02; 38,45</t>
+          <t>30,92; 38,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,09; 42,58</t>
+          <t>34,82; 42,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,28; 39,39</t>
+          <t>31,89; 39,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 42,14</t>
+          <t>38,85; 43,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,22; 33,56</t>
+          <t>28,38; 33,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,76; 36,14</t>
+          <t>30,78; 36,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,86; 32,05</t>
+          <t>26,61; 31,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,6; 35,06</t>
+          <t>32,18; 35,88</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>56090</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81089</t>
+          <t>89497</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>132572</t>
+          <t>145587</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35688; 61147</t>
+          <t>34940; 60435</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35075; 60217</t>
+          <t>35470; 62722</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23448; 45192</t>
+          <t>23704; 45721</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41994; 61995</t>
+          <t>44826; 68615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56372; 84396</t>
+          <t>54939; 82940</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61056; 92518</t>
+          <t>59679; 92095</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70124; 105384</t>
+          <t>68427; 99779</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34933; 128071</t>
+          <t>77196; 102212</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99229; 138330</t>
+          <t>96738; 135354</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101596; 141557</t>
+          <t>102097; 145729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>98775; 136254</t>
+          <t>97939; 138607</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71046; 174991</t>
+          <t>128831; 161717</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>119367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>259798</t>
+          <t>281265</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>371320</t>
+          <t>400631</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71324; 97967</t>
+          <t>71107; 99801</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86616; 121406</t>
+          <t>86863; 120256</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77892; 104389</t>
+          <t>76726; 105579</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99524; 125678</t>
+          <t>105856; 133594</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>144380; 182358</t>
+          <t>145379; 181177</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>191201; 232712</t>
+          <t>191095; 232493</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>171126; 217406</t>
+          <t>170311; 214353</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>246106; 272400</t>
+          <t>265119; 295444</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>223269; 272473</t>
+          <t>225913; 273767</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289609; 342695</t>
+          <t>290260; 343448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>258176; 312804</t>
+          <t>258181; 310305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>351491; 390440</t>
+          <t>379031; 421575</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163005</t>
+          <t>175457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>340887</t>
+          <t>370762</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>503892</t>
+          <t>546218</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>115143; 152959</t>
+          <t>114256; 153418</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>127667; 172407</t>
+          <t>127896; 172620</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105641; 143942</t>
+          <t>105867; 143017</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145589; 180902</t>
+          <t>158954; 197033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>209951; 260274</t>
+          <t>209277; 259970</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>260717; 316377</t>
+          <t>258686; 313752</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>251097; 306449</t>
+          <t>248112; 305455</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>179236; 433745</t>
+          <t>348962; 390260</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>332744; 395723</t>
+          <t>334693; 394645</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>400732; 470735</t>
+          <t>400904; 469767</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>367801; 438824</t>
+          <t>364334; 433164</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>344724; 586783</t>
+          <t>517575; 577032</t>
         </is>
       </c>
     </row>
